--- a/04-pinecastle-software-grc-program/01-enterprise-risk-assessment/artifacts/Pinecastle-Enterprise-Risk-Assessment.xlsx
+++ b/04-pinecastle-software-grc-program/01-enterprise-risk-assessment/artifacts/Pinecastle-Enterprise-Risk-Assessment.xlsx
@@ -1769,7 +1769,7 @@
         </is>
       </c>
       <c r="T2" s="37" t="n">
-        <v>46310</v>
+        <v>46315</v>
       </c>
       <c r="U2" s="30" t="inlineStr">
         <is>
@@ -1881,7 +1881,7 @@
         </is>
       </c>
       <c r="T3" s="38" t="n">
-        <v>46356</v>
+        <v>46351</v>
       </c>
       <c r="U3" s="31" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         </is>
       </c>
       <c r="T4" s="38" t="n">
-        <v>46326</v>
+        <v>46322</v>
       </c>
       <c r="U4" s="31" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="T5" s="38" t="n">
-        <v>46371</v>
+        <v>46370</v>
       </c>
       <c r="U5" s="31" t="inlineStr">
         <is>
@@ -2217,7 +2217,7 @@
         </is>
       </c>
       <c r="T6" s="38" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="U6" s="31" t="inlineStr">
         <is>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="T7" s="38" t="n">
-        <v>46402</v>
+        <v>46399</v>
       </c>
       <c r="U7" s="31" t="inlineStr">
         <is>
@@ -2441,7 +2441,7 @@
         </is>
       </c>
       <c r="T8" s="38" t="n">
-        <v>46387</v>
+        <v>46378</v>
       </c>
       <c r="U8" s="31" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="T9" s="38" t="n">
-        <v>46356</v>
+        <v>46351</v>
       </c>
       <c r="U9" s="31" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         </is>
       </c>
       <c r="T10" s="38" t="n">
-        <v>46326</v>
+        <v>46322</v>
       </c>
       <c r="U10" s="31" t="inlineStr">
         <is>
@@ -2777,7 +2777,7 @@
         </is>
       </c>
       <c r="T11" s="38" t="n">
-        <v>46357</v>
+        <v>46363</v>
       </c>
       <c r="U11" s="31" t="inlineStr">
         <is>
@@ -2889,7 +2889,7 @@
         </is>
       </c>
       <c r="T12" s="38" t="n">
-        <v>46341</v>
+        <v>46338</v>
       </c>
       <c r="U12" s="31" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="T13" s="38" t="n">
-        <v>46326</v>
+        <v>46322</v>
       </c>
       <c r="U13" s="31" t="inlineStr">
         <is>
@@ -3113,7 +3113,7 @@
         </is>
       </c>
       <c r="T14" s="38" t="n">
-        <v>46310</v>
+        <v>46315</v>
       </c>
       <c r="U14" s="31" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="T15" s="38" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="U15" s="31" t="inlineStr">
         <is>
@@ -3337,7 +3337,7 @@
         </is>
       </c>
       <c r="T16" s="38" t="n">
-        <v>46341</v>
+        <v>46338</v>
       </c>
       <c r="U16" s="31" t="inlineStr">
         <is>
@@ -3449,7 +3449,7 @@
         </is>
       </c>
       <c r="T17" s="38" t="n">
-        <v>46418</v>
+        <v>46414</v>
       </c>
       <c r="U17" s="31" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="T18" s="38" t="n">
-        <v>46446</v>
+        <v>46443</v>
       </c>
       <c r="U18" s="31" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         </is>
       </c>
       <c r="T19" s="38" t="n">
-        <v>46371</v>
+        <v>46370</v>
       </c>
       <c r="U19" s="31" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="T20" s="38" t="n">
-        <v>46326</v>
+        <v>46322</v>
       </c>
       <c r="U20" s="31" t="inlineStr">
         <is>
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="T21" s="39" t="n">
-        <v>46387</v>
+        <v>46378</v>
       </c>
       <c r="U21" s="32" t="inlineStr">
         <is>
@@ -4009,7 +4009,7 @@
         </is>
       </c>
       <c r="T22" s="39" t="n">
-        <v>46477</v>
+        <v>46472</v>
       </c>
       <c r="U22" s="32" t="inlineStr">
         <is>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="T23" s="39" t="n">
-        <v>46416</v>
+        <v>46413</v>
       </c>
       <c r="U23" s="32" t="inlineStr">
         <is>
@@ -4248,7 +4248,7 @@
         </is>
       </c>
       <c r="E2" s="37" t="n">
-        <v>46310</v>
+        <v>46315</v>
       </c>
       <c r="F2" s="30" t="inlineStr">
         <is>
@@ -4286,7 +4286,7 @@
         </is>
       </c>
       <c r="E3" s="38" t="n">
-        <v>46356</v>
+        <v>46351</v>
       </c>
       <c r="F3" s="31" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         </is>
       </c>
       <c r="E4" s="38" t="n">
-        <v>46326</v>
+        <v>46322</v>
       </c>
       <c r="F4" s="31" t="inlineStr">
         <is>
@@ -4362,7 +4362,7 @@
         </is>
       </c>
       <c r="E5" s="38" t="n">
-        <v>46371</v>
+        <v>46370</v>
       </c>
       <c r="F5" s="31" t="inlineStr">
         <is>
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="E6" s="38" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="F6" s="31" t="inlineStr">
         <is>
@@ -4438,7 +4438,7 @@
         </is>
       </c>
       <c r="E7" s="38" t="n">
-        <v>46402</v>
+        <v>46399</v>
       </c>
       <c r="F7" s="31" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         </is>
       </c>
       <c r="E8" s="38" t="n">
-        <v>46387</v>
+        <v>46378</v>
       </c>
       <c r="F8" s="31" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         </is>
       </c>
       <c r="E9" s="38" t="n">
-        <v>46356</v>
+        <v>46351</v>
       </c>
       <c r="F9" s="31" t="inlineStr">
         <is>
@@ -4552,7 +4552,7 @@
         </is>
       </c>
       <c r="E10" s="38" t="n">
-        <v>46326</v>
+        <v>46322</v>
       </c>
       <c r="F10" s="31" t="inlineStr">
         <is>
@@ -4590,7 +4590,7 @@
         </is>
       </c>
       <c r="E11" s="38" t="n">
-        <v>46357</v>
+        <v>46363</v>
       </c>
       <c r="F11" s="31" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
         </is>
       </c>
       <c r="E12" s="38" t="n">
-        <v>46341</v>
+        <v>46338</v>
       </c>
       <c r="F12" s="31" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         </is>
       </c>
       <c r="E13" s="38" t="n">
-        <v>46326</v>
+        <v>46322</v>
       </c>
       <c r="F13" s="31" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         </is>
       </c>
       <c r="E14" s="38" t="n">
-        <v>46310</v>
+        <v>46315</v>
       </c>
       <c r="F14" s="31" t="inlineStr">
         <is>
@@ -4742,7 +4742,7 @@
         </is>
       </c>
       <c r="E15" s="38" t="n">
-        <v>46295</v>
+        <v>46290</v>
       </c>
       <c r="F15" s="31" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="E16" s="38" t="n">
-        <v>46341</v>
+        <v>46338</v>
       </c>
       <c r="F16" s="31" t="inlineStr">
         <is>
@@ -4818,7 +4818,7 @@
         </is>
       </c>
       <c r="E17" s="38" t="n">
-        <v>46418</v>
+        <v>46414</v>
       </c>
       <c r="F17" s="31" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         </is>
       </c>
       <c r="E18" s="38" t="n">
-        <v>46446</v>
+        <v>46443</v>
       </c>
       <c r="F18" s="31" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         </is>
       </c>
       <c r="E19" s="38" t="n">
-        <v>46371</v>
+        <v>46370</v>
       </c>
       <c r="F19" s="31" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="E20" s="38" t="n">
-        <v>46326</v>
+        <v>46322</v>
       </c>
       <c r="F20" s="31" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         </is>
       </c>
       <c r="E21" s="39" t="n">
-        <v>46387</v>
+        <v>46378</v>
       </c>
       <c r="F21" s="32" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         </is>
       </c>
       <c r="E22" s="38" t="n">
-        <v>46477</v>
+        <v>46472</v>
       </c>
       <c r="F22" s="31" t="inlineStr">
         <is>
@@ -5046,7 +5046,7 @@
         </is>
       </c>
       <c r="E23" s="38" t="n">
-        <v>46416</v>
+        <v>46413</v>
       </c>
       <c r="F23" s="31" t="inlineStr">
         <is>
